--- a/Bauteillisten/Bestellliste_DigiKey_V5.xlsx
+++ b/Bauteillisten/Bestellliste_DigiKey_V5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janne\Documents\GitHub\active-balancing\Bauteillisten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD806745-6B46-443C-8A18-C500181658B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2A4C314-E352-47CB-A53C-0D586CD229AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="155">
   <si>
     <t>DigiKey - Warenkorb</t>
   </si>
@@ -485,19 +485,13 @@
   </si>
   <si>
     <t>RES 330</t>
-  </si>
-  <si>
-    <t>RES 10MEG</t>
-  </si>
-  <si>
-    <t>Müssen wir absprechen, ob wir die nehmen, oder die 330 und 10MEG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -506,17 +500,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0" tint="-0.34998626667073579"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -551,7 +534,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -564,11 +547,6 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -883,7 +861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="6.77734375" customWidth="1"/>
@@ -1644,12 +1622,7 @@
       <c r="J24" s="9">
         <v>1.33</v>
       </c>
-      <c r="K24" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="L24" s="11" t="s">
-        <v>156</v>
-      </c>
+      <c r="L24" s="8"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
@@ -1680,9 +1653,7 @@
       <c r="J25" s="9">
         <v>1.22</v>
       </c>
-      <c r="K25" s="10" t="s">
-        <v>151</v>
-      </c>
+      <c r="L25" s="8"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
@@ -1973,35 +1944,35 @@
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="12">
+      <c r="A35" s="7">
         <v>33</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="7">
         <v>4</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="F35" s="13"/>
-      <c r="G35" s="12">
+      <c r="F35" s="8"/>
+      <c r="G35" s="7">
         <v>4</v>
       </c>
-      <c r="H35" s="12">
-        <v>0</v>
-      </c>
-      <c r="I35" s="13">
+      <c r="H35" s="7">
+        <v>0</v>
+      </c>
+      <c r="I35" s="8">
         <v>0.52</v>
       </c>
-      <c r="J35" s="14">
+      <c r="J35" s="9">
         <v>2.08</v>
       </c>
-      <c r="K35" s="13"/>
+      <c r="K35" s="8"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
@@ -2470,7 +2441,7 @@
         <v>49</v>
       </c>
       <c r="B53" s="2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E53" t="s">
         <v>153</v>
@@ -2484,26 +2455,12 @@
         <v>50</v>
       </c>
       <c r="B54" s="2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E54" t="s">
         <v>154</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A55" s="2">
-        <v>51</v>
-      </c>
-      <c r="B55" s="2">
-        <v>50</v>
-      </c>
-      <c r="E55" t="s">
-        <v>155</v>
-      </c>
-      <c r="K55" s="6" t="s">
         <v>151</v>
       </c>
     </row>
